--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.68380284944735</v>
+        <v>6.123617963035195</v>
       </c>
       <c r="D2" t="n">
-        <v>24.38237068047322</v>
+        <v>3.962135235576898</v>
       </c>
       <c r="E2" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F2" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.70877580911175</v>
+        <v>3.852676068980659</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62077013859466</v>
+        <v>2.700875147521633</v>
       </c>
       <c r="E3" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F3" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.75532087733774</v>
+        <v>6.947739642567383</v>
       </c>
       <c r="D4" t="n">
-        <v>33.53356527421443</v>
+        <v>5.449204357059846</v>
       </c>
       <c r="E4" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.72139393610841</v>
+        <v>7.267226514617617</v>
       </c>
       <c r="D5" t="n">
-        <v>40.36059444649333</v>
+        <v>6.558596597555167</v>
       </c>
       <c r="E5" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F5" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.1878194576509</v>
+        <v>4.093020661868272</v>
       </c>
       <c r="D6" t="n">
-        <v>24.90163024898327</v>
+        <v>4.046514915459781</v>
       </c>
       <c r="E6" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F6" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.95667508527308</v>
+        <v>7.467959701356876</v>
       </c>
       <c r="D7" t="n">
-        <v>45.68282780274785</v>
+        <v>7.423459517946526</v>
       </c>
       <c r="E7" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F7" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.17538407727012</v>
+        <v>7.990999912556394</v>
       </c>
       <c r="D8" t="n">
-        <v>48.69975826068242</v>
+        <v>7.913710717360894</v>
       </c>
       <c r="E8" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F8" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.54700877982147</v>
+        <v>7.23888892672099</v>
       </c>
       <c r="D9" t="n">
-        <v>44.08488709550735</v>
+        <v>7.163794153019944</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F9" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.46346080051061</v>
+        <v>7.225312380082975</v>
       </c>
       <c r="D10" t="n">
-        <v>44.05268612575556</v>
+        <v>7.158561495435279</v>
       </c>
       <c r="E10" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F10" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.10011405349656</v>
+        <v>10.09126853369319</v>
       </c>
       <c r="D11" t="n">
-        <v>61.79820078118915</v>
+        <v>10.04220762694324</v>
       </c>
       <c r="E11" t="n">
-        <v>10.61850863472121</v>
+        <v>1.725507653142197</v>
       </c>
       <c r="F11" t="n">
-        <v>12.85080042407878</v>
+        <v>2.088255068912802</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
